--- a/outputs/37378.xlsx
+++ b/outputs/37378.xlsx
@@ -108,12 +108,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -309,58 +313,58 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="4.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="4.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <f aca="false">IF(B2="","",COUNTA($B$2:B2))</f>
+      <c r="A2" s="2" t="n">
+        <f aca="false">IF(B2&lt;&gt;"",COUNTA($B$2:B2),"")</f>
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>2252</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <f aca="false">IF(B3="","",COUNTA($B$2:B3))</f>
+      <c r="A3" s="2" t="n">
+        <f aca="false">IF(B3&lt;&gt;"",COUNTA($B$2:B3),"")</f>
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <f aca="false">IF(B4="","",COUNTA($B$2:B4))</f>
+      <c r="A4" s="2" t="n">
+        <f aca="false">IF(B4&lt;&gt;"",COUNTA($B$2:B4),"")</f>
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="str">
-        <f aca="false">IF(B5="","",COUNTA($B$2:B5))</f>
+      <c r="A5" s="2" t="str">
+        <f aca="false">IF(B5&lt;&gt;"",COUNTA($B$2:B5),"")</f>
         <v/>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="str">
-        <f aca="false">IF(B6="","",COUNTA($B$2:B6))</f>
+      <c r="A6" s="2" t="str">
+        <f aca="false">IF(B6&lt;&gt;"",COUNTA($B$2:B6),"")</f>
         <v/>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/37378.xlsx
+++ b/outputs/37378.xlsx
@@ -327,7 +327,7 @@
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
-        <f aca="false">IF(B2&lt;&gt;"",COUNTA($B$2:B2),"")</f>
+        <f aca="false">IF(B2&lt;&gt;"",ROW()-1,"")</f>
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
@@ -336,7 +336,7 @@
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
-        <f aca="false">IF(B3&lt;&gt;"",COUNTA($B$2:B3),"")</f>
+        <f aca="false">IF(B3&lt;&gt;"",ROW()-1,"")</f>
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -345,7 +345,7 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
-        <f aca="false">IF(B4&lt;&gt;"",COUNTA($B$2:B4),"")</f>
+        <f aca="false">IF(B4&lt;&gt;"",ROW()-1,"")</f>
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
@@ -354,14 +354,14 @@
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="str">
-        <f aca="false">IF(B5&lt;&gt;"",COUNTA($B$2:B5),"")</f>
+        <f aca="false">IF(B5&lt;&gt;"",ROW()-1,"")</f>
         <v/>
       </c>
       <c r="B5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="str">
-        <f aca="false">IF(B6&lt;&gt;"",COUNTA($B$2:B6),"")</f>
+        <f aca="false">IF(B6&lt;&gt;"",ROW()-1,"")</f>
         <v/>
       </c>
       <c r="B6" s="2"/>
